--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-09-2025.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£12.12</t>
+          <t>£13.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£18.00</t>
+          <t>£16.62</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£24.48</t>
+          <t>£23.00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>£24.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£25.00</t>
+          <t>£26.58</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£27.62</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£41.18</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>£44.00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£46.88</t>
+          <t>£46.00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£48.99</t>
+          <t>£46.88</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£33.33</t>
+          <t>£30.00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£40.00</t>
+          <t>£38.00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>£53.33</t>
+          <t>£48.00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
